--- a/Quizres.xlsx
+++ b/Quizres.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="30">
   <si>
     <t>Informazioni cronologiche</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>deep ast</t>
+  </si>
+  <si>
+    <t>base/pr</t>
+  </si>
+  <si>
+    <t>delta ppl</t>
+  </si>
+  <si>
+    <t>delta ppl ast</t>
   </si>
 </sst>
 </file>
@@ -442,25 +451,25 @@
         <v>14.0</v>
       </c>
       <c r="Q2" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="R2" s="3">
         <v>16.0</v>
       </c>
-      <c r="R2" s="3">
+      <c r="S2" s="3">
         <v>17.0</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="3">
         <v>18.0</v>
       </c>
-      <c r="T2" s="3">
+      <c r="U2" s="3">
         <v>19.0</v>
       </c>
-      <c r="U2" s="3">
+      <c r="V2" s="3">
         <v>20.0</v>
       </c>
-      <c r="V2" s="3">
+      <c r="W2" s="3">
         <v>21.0</v>
-      </c>
-      <c r="W2" s="3">
-        <v>22.0</v>
       </c>
     </row>
     <row r="3">
@@ -2190,6 +2199,171 @@
       <c r="W31" s="7">
         <f t="shared" si="9"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="7">
+        <f t="shared" ref="C35:Q35" si="10">if(C19="BASE", 0, 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="F35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="G35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="J35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K35" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="N35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O35" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="Q35" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-0.0156</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.0156</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="6">
+        <v>-0.0468</v>
+      </c>
+      <c r="I36" s="6">
+        <v>-0.039</v>
+      </c>
+      <c r="J36" s="6">
+        <v>-0.0156</v>
+      </c>
+      <c r="K36" s="6">
+        <v>-0.5312</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.0156</v>
+      </c>
+      <c r="M36" s="6">
+        <v>-0.0312</v>
+      </c>
+      <c r="N36" s="6">
+        <v>-0.0312</v>
+      </c>
+      <c r="O36" s="6">
+        <v>0.0312</v>
+      </c>
+      <c r="P36" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-0.1875</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.0312</v>
+      </c>
+      <c r="F37" s="6">
+        <v>-0.0312</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="6">
+        <v>-0.0781</v>
+      </c>
+      <c r="I37" s="6">
+        <v>0.0156</v>
+      </c>
+      <c r="J37" s="6">
+        <v>-0.0156</v>
+      </c>
+      <c r="K37" s="6">
+        <v>-0.3203</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="M37" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="6">
+        <v>-0.0312</v>
+      </c>
+      <c r="O37" s="6">
+        <v>0.0439</v>
+      </c>
+      <c r="P37" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
